--- a/artfynd/A 31476-2025 artfynd.xlsx
+++ b/artfynd/A 31476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316700</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605202</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,6 +1185,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316533</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316878</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316689</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1454,6 +1494,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316886</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1552,6 +1597,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317015</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317137</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316529</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316695</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589818</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589990</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605452</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605981</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605345</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594509</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595459</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595814</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604965</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605363</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607381</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3011,6 +3131,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317293</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3108,6 +3233,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589760</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3205,6 +3335,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589868</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3302,6 +3437,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589961</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3399,6 +3539,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590109</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3496,6 +3641,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590145</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3593,6 +3743,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119593289</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3690,6 +3845,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119593356</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3787,6 +3947,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119593479</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3884,6 +4049,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119593987</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3981,6 +4151,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594040</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4078,6 +4253,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594095</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4175,6 +4355,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594384</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4272,6 +4457,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595769</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4369,6 +4559,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595839</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4466,6 +4661,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595859</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4563,6 +4763,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595947</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4660,6 +4865,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605062</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4757,6 +4967,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605339</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4854,6 +5069,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605983</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4951,6 +5171,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607335</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5048,6 +5273,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607416</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5146,6 +5376,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316464</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5244,6 +5479,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317022</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5342,6 +5582,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317205</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5439,6 +5684,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589772</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5536,6 +5786,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594626</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5633,6 +5888,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605581</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5730,6 +5990,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589953</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5827,6 +6092,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590258</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5924,6 +6194,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119593455</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6021,6 +6296,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596212</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6118,6 +6398,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605409</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6215,6 +6500,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607611</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6312,6 +6602,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589977</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6409,6 +6704,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596085</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6506,6 +6806,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605197</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6603,6 +6908,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595382</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6700,6 +7010,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594862</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6797,6 +7112,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605803</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6895,6 +7215,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316377</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6992,6 +7317,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119589809</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7090,6 +7420,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316439</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7188,6 +7523,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316705</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7286,6 +7626,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87316871</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7384,6 +7729,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317313</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7481,6 +7831,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594962</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7578,6 +7933,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119595104</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7675,6 +8035,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607190</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7773,6 +8138,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317213</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7871,6 +8241,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87317358</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7968,6 +8343,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594067</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8065,6 +8445,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119594838</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8162,8 +8547,92 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119607299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>